--- a/staff_forms/005_day_camp_staff_health_screening_form--staff_forms.xlsx
+++ b/staff_forms/005_day_camp_staff_health_screening_form--staff_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>health_screening_question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>health_screening_question_1_choices</t>
+          <t>health_screening_question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,29 +1216,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>health_screening_question_2_choices</t>
+          <t>health_screening_question_8_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>health_screening_question_8_choices</t>
+          <t>health_screening_question_9_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>health_screening_question_9_choices</t>
+          <t>health_screening_question_10_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
     </row>
@@ -1369,27 +1369,10 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>health_screening_question_10_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>None</t>
         </is>
